--- a/classes.xlsx
+++ b/classes.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tobychan/Library/Application Support/eMed/eMed upgrade/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tobychan/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D82D18C7-EA9F-9743-B5DA-AFB0C2FBE7EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCAE4E4C-69F4-E34C-84C8-7F8E2A37E1D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22240" yWindow="500" windowWidth="16160" windowHeight="17500" xr2:uid="{3187FA12-9468-D749-A226-2B99DCD8678D}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1697" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1690" uniqueCount="352">
   <si>
     <t>start</t>
   </si>
@@ -1096,27 +1096,6 @@
   </si>
   <si>
     <t>Y1&amp;2 Prac exams</t>
-  </si>
-  <si>
-    <t>https://emed.med.unsw.edu.au/Map.nsf/by_unid/D948A8D4B4D22AEBCA257D8F00046E34/$FILE/AEB.S.Neurodegen.L.Neurodegen_26_SK.pdf</t>
-  </si>
-  <si>
-    <t>https://emed.med.unsw.edu.au/Map.nsf/by_unid/1526DA21BFC93C49CA25733900062AE4/$FILE/AEB.S.Neurodegen.L.Decisions_26_LS.pdf</t>
-  </si>
-  <si>
-    <t>https://emed.med.unsw.edu.au/Map.nsf/by_unid/BFBF4FAF115DD14CCA25733900062D84/$FILE/AEB.S.Neurodegen.L.PhrmNeuroD_26_NK.pdf</t>
-  </si>
-  <si>
-    <t>slides</t>
-  </si>
-  <si>
-    <t>https://emed.med.unsw.edu.au/Map.nsf/by_unid/90E6B24D286D5903CA25733900062ACE/$FILE/AEB.S.StrokeScen.L.HCF1SlpLan_26_FA.pdf</t>
-  </si>
-  <si>
-    <t>https://emed.med.unsw.edu.au/Map.nsf/by_unid/58D0B05E984684B7CA25733900062AF2/$FILE/AEB.S.StrokeScen.L.Cerebellum_26_TD.pdf</t>
-  </si>
-  <si>
-    <t>https://emed.med.unsw.edu.au/Map.nsf/by_unid/47B4A684F06E6419CA25733900062AB7/$FILE/AEB.S.Neurodegen.L.Parkinsns_26_JC.pdf</t>
   </si>
 </sst>
 </file>
@@ -1627,9 +1606,7 @@
       <c r="I1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="5" t="s">
-        <v>355</v>
-      </c>
+      <c r="J1" s="5"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
@@ -6961,7 +6938,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="193" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="1" t="s">
         <v>8</v>
       </c>
@@ -6990,7 +6967,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="194" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="1" t="s">
         <v>8</v>
       </c>
@@ -7019,7 +6996,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="195" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="1" t="s">
         <v>8</v>
       </c>
@@ -7045,7 +7022,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="196" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="1" t="s">
         <v>8</v>
       </c>
@@ -7070,11 +7047,8 @@
       <c r="I196" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="J196" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="197" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="197" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="1" t="s">
         <v>8</v>
       </c>
@@ -7099,11 +7073,8 @@
       <c r="I197" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="J197" s="1" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="198" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="198" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="1" t="s">
         <v>8</v>
       </c>
@@ -7129,7 +7100,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="199" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="1" t="s">
         <v>8</v>
       </c>
@@ -7155,7 +7126,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="200" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="1" t="s">
         <v>8</v>
       </c>
@@ -7181,7 +7152,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="201" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="1" t="s">
         <v>8</v>
       </c>
@@ -7210,7 +7181,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="202" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="1" t="s">
         <v>8</v>
       </c>
@@ -7239,7 +7210,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="203" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="1" t="s">
         <v>8</v>
       </c>
@@ -7265,7 +7236,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="204" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="1" t="s">
         <v>8</v>
       </c>
@@ -7294,7 +7265,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="205" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="1" t="s">
         <v>8</v>
       </c>
@@ -7323,7 +7294,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="206" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="1" t="s">
         <v>8</v>
       </c>
@@ -7349,7 +7320,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="207" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="1" t="s">
         <v>8</v>
       </c>
@@ -7374,11 +7345,8 @@
       <c r="I207" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J207" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="208" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="208" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="1" t="s">
         <v>8</v>
       </c>
@@ -7404,7 +7372,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="209" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="1" t="s">
         <v>8</v>
       </c>
@@ -7430,7 +7398,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="210" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="1" t="s">
         <v>8</v>
       </c>
@@ -7459,7 +7427,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="211" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="1" t="s">
         <v>8</v>
       </c>
@@ -7488,7 +7456,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="212" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="1" t="s">
         <v>8</v>
       </c>
@@ -7514,7 +7482,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="213" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="1" t="s">
         <v>8</v>
       </c>
@@ -7543,7 +7511,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="214" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="1" t="s">
         <v>8</v>
       </c>
@@ -7572,7 +7540,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="215" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="1" t="s">
         <v>8</v>
       </c>
@@ -7597,11 +7565,8 @@
       <c r="I215" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J215" s="1" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="216" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="216" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="1" t="s">
         <v>8</v>
       </c>
@@ -7626,11 +7591,8 @@
       <c r="I216" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J216" s="1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="217" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="217" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="1" t="s">
         <v>8</v>
       </c>
@@ -7655,11 +7617,8 @@
       <c r="I217" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J217" s="1" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="218" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="218" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="1" t="s">
         <v>8</v>
       </c>
@@ -7685,7 +7644,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="219" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="1" t="s">
         <v>8</v>
       </c>
@@ -7711,7 +7670,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="220" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="1" t="s">
         <v>8</v>
       </c>
@@ -7740,7 +7699,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="221" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="1" t="s">
         <v>8</v>
       </c>
@@ -7769,7 +7728,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="222" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="1" t="s">
         <v>8</v>
       </c>
@@ -7798,7 +7757,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="223" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="1" t="s">
         <v>8</v>
       </c>
@@ -7827,7 +7786,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="224" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="1" t="s">
         <v>8</v>
       </c>

--- a/classes.xlsx
+++ b/classes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tobychan/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCAE4E4C-69F4-E34C-84C8-7F8E2A37E1D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{780156C0-F4EE-1946-A20A-58CC4DC9A7FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22240" yWindow="500" windowWidth="16160" windowHeight="17500" xr2:uid="{3187FA12-9468-D749-A226-2B99DCD8678D}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1690" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1691" uniqueCount="352">
   <si>
     <t>start</t>
   </si>
@@ -9495,6 +9495,9 @@
       <c r="G286" s="1" t="s">
         <v>339</v>
       </c>
+      <c r="I286" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="287" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="1" t="s">
